--- a/data_raw/data_raw_2024_sheets/LTER5_OR_T03_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER5_OR_T03_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CC62C3-3355-F343-9CDB-041A076460D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67BBBC81-F68E-CF45-B0F2-1EC23033BE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1540" windowWidth="38860" windowHeight="27260" xr2:uid="{A8AB995C-9280-C345-95ED-2061CFE661B1}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="18780" xr2:uid="{A8AB995C-9280-C345-95ED-2061CFE661B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="86">
   <si>
     <t>LTER5</t>
   </si>
@@ -360,56 +360,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD4A6FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <font>
         <sz val="11"/>
@@ -418,7 +369,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF159FEC"/>
+          <bgColor rgb="FFFFA500"/>
         </patternFill>
       </fill>
     </dxf>
@@ -430,7 +381,296 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF17A43F"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4A6FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -442,7 +682,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF006400"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -454,7 +694,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFB0006"/>
+          <bgColor rgb="FFA1BCD6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -478,7 +718,19 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFA1BCD6"/>
+          <bgColor rgb="FFFB0006"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF006400"/>
         </patternFill>
       </fill>
     </dxf>
@@ -490,19 +742,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFB07EDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
+          <bgColor rgb="FF17A43F"/>
         </patternFill>
       </fill>
     </dxf>
@@ -514,7 +754,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFB07EDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -526,7 +766,38 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF159FEC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFA500"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -540,7 +811,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF49900"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -548,13 +819,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF49900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2390,6 +2654,15 @@
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
       <c r="D37" t="s">
         <v>3</v>
       </c>
@@ -2416,6 +2689,15 @@
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2</v>
+      </c>
       <c r="D38" t="s">
         <v>3</v>
       </c>
@@ -2442,6 +2724,15 @@
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" t="s">
         <v>26</v>
       </c>
@@ -2468,6 +2759,15 @@
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
       <c r="D40" t="s">
         <v>3</v>
       </c>
@@ -2494,6 +2794,15 @@
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
       <c r="D41" t="s">
         <v>3</v>
       </c>
@@ -2520,6 +2829,15 @@
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
       <c r="D42" t="s">
         <v>3</v>
       </c>
@@ -2546,6 +2864,15 @@
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
       <c r="D43" t="s">
         <v>3</v>
       </c>
@@ -2572,6 +2899,15 @@
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
       <c r="D44" t="s">
         <v>26</v>
       </c>
@@ -2598,6 +2934,15 @@
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2</v>
+      </c>
       <c r="D45" t="s">
         <v>3</v>
       </c>
@@ -2624,6 +2969,15 @@
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2</v>
+      </c>
       <c r="D46" t="s">
         <v>3</v>
       </c>
@@ -2650,6 +3004,15 @@
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
       <c r="D47" t="s">
         <v>26</v>
       </c>
@@ -2676,6 +3039,15 @@
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
       <c r="D48" t="s">
         <v>3</v>
       </c>
@@ -2701,7 +3073,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
       <c r="D49" t="s">
         <v>3</v>
       </c>
@@ -2727,7 +3108,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="4:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2</v>
+      </c>
       <c r="D50" t="s">
         <v>3</v>
       </c>
@@ -2755,78 +3145,166 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G2 I2:K2">
-    <cfRule type="beginsWith" dxfId="20" priority="10" operator="beginsWith" text="FI">
+    <cfRule type="containsText" dxfId="42" priority="33" operator="containsText" text="Missing data">
+      <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="41" priority="32" operator="beginsWith" text="FI">
       <formula>LEFT(A2,LEN("FI"))="FI"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="Missing data">
-      <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:G2">
-    <cfRule type="beginsWith" dxfId="18" priority="8" operator="beginsWith" text="UK">
+    <cfRule type="beginsWith" dxfId="40" priority="31" operator="beginsWith" text="FU">
+      <formula>LEFT(A2,LEN("FU"))="FU"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="39" priority="30" operator="beginsWith" text="UK">
       <formula>LEFT(A2,LEN("UK"))="UK"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="17" priority="9" operator="beginsWith" text="FU">
-      <formula>LEFT(A2,LEN("FU"))="FU"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:K36 L43:M43 D37:G50">
-    <cfRule type="expression" dxfId="16" priority="12">
+  <conditionalFormatting sqref="A3:K36 D37:G50 L43:M43">
+    <cfRule type="expression" dxfId="38" priority="35">
+      <formula>A3="Na"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="34">
       <formula>A3="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:K36">
-    <cfRule type="containsText" dxfId="14" priority="14" operator="containsText" text=",">
+    <cfRule type="expression" dxfId="36" priority="43">
+      <formula>H3="Recruitment"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="35" priority="37" operator="beginsWith" text="Fusion">
+      <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="42">
+      <formula>H3="Growth"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="41">
+      <formula>H3="Shrinkage"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="40">
+      <formula>H3="Death"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="39">
+      <formula>H3="Missing Data"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="30" priority="38" operator="beginsWith" text="Fission">
+      <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="29" priority="36" operator="containsText" text=",">
       <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="13" priority="15" operator="beginsWith" text="Fusion">
-      <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="12" priority="16" operator="beginsWith" text="Fission">
-      <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="17">
-      <formula>H3="Missing Data"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="18">
-      <formula>H3="Death"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="19">
-      <formula>H3="Shrinkage"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="20">
-      <formula>H3="Growth"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="21">
-      <formula>H3="Recruitment"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:P2">
-    <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="UK">
+    <cfRule type="beginsWith" dxfId="28" priority="23" operator="beginsWith" text="UK">
       <formula>LEFT(I2,LEN("UK"))="UK"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="5" priority="7" operator="beginsWith" text="FU">
+    <cfRule type="beginsWith" dxfId="27" priority="29" operator="beginsWith" text="FU">
       <formula>LEFT(I2,LEN("FU"))="FU"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:P2">
-    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="26" priority="24" operator="beginsWith" text="FI">
       <formula>LEFT(L2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",L2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="4" operator="beginsWith" text="R">
+    <cfRule type="beginsWith" dxfId="24" priority="26" operator="beginsWith" text="R">
       <formula>LEFT(L2,LEN("R"))="R"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="D">
+    <cfRule type="containsText" dxfId="22" priority="28" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>A37="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>A37="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>A38="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>A38="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>A39="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>A39="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>A40="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>A40="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:A43">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>A41="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>A41="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="expression" dxfId="11" priority="11">
+      <formula>A44="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="12">
+      <formula>A44="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>A45="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>A45="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>A46="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>A46="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47:A50">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>A47="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>A47="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37:B53">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>B37="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>B37="Na"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:C50">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C37="UK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C37="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
